--- a/nriss-patch-2/ig/StructureDefinition-fr-location-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-location-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="418">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}inv-location-type-chambre:Location Type Chambre {extension('http://fhir.fr/StructureDefinition/fr-core-location-type-chambre').exists() implies type.coding.where(code = 'CHAMB').exists()}inv-location-type-lit:Location Type Lit {extension('http://fhir.fr/StructureDefinition/fr-core-location-position-lit').exists() implies type.coding.where(code = 'LIT').exists()}</t>
   </si>
   <si>
     <t>.Role[classCode=SDLC]</t>
@@ -615,23 +615,42 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>Location.extension:usePeriod</t>
-  </si>
-  <si>
-    <t>usePeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-use-period|2.1.0}
+    <t>Location.extension:typeChambre</t>
+  </si>
+  <si>
+    <t>typeChambre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location-type-chambre|2.2.0}
 </t>
   </si>
   <si>
-    <t>FR Core Use Period Extension</t>
+    <t>FR Core Location Extension - Type de chambre</t>
+  </si>
+  <si>
+    <t>Type de chambre</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Location.extension:positionLit</t>
+  </si>
+  <si>
+    <t>positionLit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location-position-lit|2.2.0}
+</t>
+  </si>
+  <si>
+    <t>FR Core Location Extension - Position du lit</t>
+  </si>
+  <si>
+    <t>Position du lit dans la chambre</t>
+  </si>
+  <si>
     <t>Location.modifierExtension</t>
   </si>
   <si>
@@ -655,7 +674,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant fonctionnel du lieu. Il est recommandé de remplir ce champs pour faciliter l'identification des ressources.</t>
+    <t>Unique code or number identifying the location to its users</t>
   </si>
   <si>
     <t>Unique code or number identifying the location to its users.</t>
@@ -670,269 +689,129 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>Location.identifier.id</t>
-  </si>
-  <si>
-    <t>Location.identifier.extension</t>
-  </si>
-  <si>
-    <t>Location.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>Location.status</t>
+  </si>
+  <si>
+    <t>active | suspended | inactive</t>
+  </si>
+  <si>
+    <t>The status property covers the general availability of the resource, not the current value which may be covered by the operationStatus, or by a schedule/slots if they are configured for the location.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Location.identifier.type</t>
+    <t>Indicates whether the location is still in use.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/location-status|4.0.1</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Location.operationalStatus</t>
+  </si>
+  <si>
+    <t>The operational status of the location (typically only for a bed/room)</t>
+  </si>
+  <si>
+    <t>The operational status covers operation values most relevant to beds (but can also apply to rooms/units/chairs/etc. such as an isolation unit/dialysis chair). This typically covers concepts such as contamination, housekeeping, and other activities like maintenance.</t>
+  </si>
+  <si>
+    <t>The operational status if the location (where typically a bed/room).</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0116|3.0.0</t>
+  </si>
+  <si>
+    <t>Location.name</t>
+  </si>
+  <si>
+    <t>Nom de la structure</t>
+  </si>
+  <si>
+    <t>Name of the location as used by humans. Does not need to be unique.</t>
+  </si>
+  <si>
+    <t>If the name of a location changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
+  </si>
+  <si>
+    <t>.name</t>
+  </si>
+  <si>
+    <t>Location.alias</t>
+  </si>
+  <si>
+    <t>A list of alternate names that the location is known as, or was known as, in the past</t>
+  </si>
+  <si>
+    <t>A list of alternate names that the location is known as, or was known as, in the past.</t>
+  </si>
+  <si>
+    <t>There are no dates associated with the alias/historic names, as this is not intended to track when names were used, but to assist in searching so that older names can still result in identifying the location.</t>
+  </si>
+  <si>
+    <t>Over time locations and organizations go through many changes and can be known by different names.
+For searching knowing previous names that the location was known by can be very useful.</t>
+  </si>
+  <si>
+    <t>Location.description</t>
+  </si>
+  <si>
+    <t>Additional details about the location that could be displayed as further information to identify the location beyond its name</t>
+  </si>
+  <si>
+    <t>Description of the Location, which helps in finding or referencing the place.</t>
+  </si>
+  <si>
+    <t>Humans need additional information to verify a correct location has been identified.</t>
+  </si>
+  <si>
+    <t>.playingEntity[classCode=PLC determinerCode=INSTANCE].desc</t>
+  </si>
+  <si>
+    <t>Location.mode</t>
+  </si>
+  <si>
+    <t>instance | kind</t>
+  </si>
+  <si>
+    <t>Indicates whether a resource instance represents a specific location or a class of locations.</t>
+  </si>
+  <si>
+    <t>This is labeled as a modifier because whether or not the location is a class of locations changes how it can be used and understood.</t>
+  </si>
+  <si>
+    <t>When using a Location resource for scheduling or orders, we need to be able to refer to a class of Locations instead of a specific Location.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/location-mode|4.0.1</t>
+  </si>
+  <si>
+    <t>.playingEntity[classCode=PLC].determinerCode</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Location.type</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-identifier-type|2.1.0</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>Location.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>Location.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>Location.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>Location.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>Location.status</t>
-  </si>
-  <si>
-    <t>active | suspended | inactive</t>
-  </si>
-  <si>
-    <t>The status property covers the general availability of the resource, not the current value which may be covered by the operationStatus, or by a schedule/slots if they are configured for the location.</t>
-  </si>
-  <si>
-    <t>Indicates whether the location is still in use.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/location-status|4.0.1</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Location.operationalStatus</t>
-  </si>
-  <si>
-    <t>The operational status of the location (typically only for a bed/room)</t>
-  </si>
-  <si>
-    <t>The operational status covers operation values most relevant to beds (but can also apply to rooms/units/chairs/etc. such as an isolation unit/dialysis chair). This typically covers concepts such as contamination, housekeeping, and other activities like maintenance.</t>
-  </si>
-  <si>
-    <t>The operational status if the location (where typically a bed/room).</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0116|3.0.0</t>
-  </si>
-  <si>
-    <t>Location.name</t>
-  </si>
-  <si>
-    <t>Nom de la structure</t>
-  </si>
-  <si>
-    <t>Name of the location as used by humans. Does not need to be unique.</t>
-  </si>
-  <si>
-    <t>If the name of a location changes, consider putting the old name in the alias column so that it can still be located through searches.</t>
-  </si>
-  <si>
-    <t>.name</t>
-  </si>
-  <si>
-    <t>Location.alias</t>
-  </si>
-  <si>
-    <t>A list of alternate names that the location is known as, or was known as, in the past</t>
-  </si>
-  <si>
-    <t>A list of alternate names that the location is known as, or was known as, in the past.</t>
-  </si>
-  <si>
-    <t>There are no dates associated with the alias/historic names, as this is not intended to track when names were used, but to assist in searching so that older names can still result in identifying the location.</t>
-  </si>
-  <si>
-    <t>Over time locations and organizations go through many changes and can be known by different names.
-For searching knowing previous names that the location was known by can be very useful.</t>
-  </si>
-  <si>
-    <t>Location.description</t>
-  </si>
-  <si>
-    <t>Additional details about the location that could be displayed as further information to identify the location beyond its name</t>
-  </si>
-  <si>
-    <t>Description of the Location, which helps in finding or referencing the place.</t>
-  </si>
-  <si>
-    <t>Humans need additional information to verify a correct location has been identified.</t>
-  </si>
-  <si>
-    <t>.playingEntity[classCode=PLC determinerCode=INSTANCE].desc</t>
-  </si>
-  <si>
-    <t>Location.mode</t>
-  </si>
-  <si>
-    <t>instance | kind</t>
-  </si>
-  <si>
-    <t>Indicates whether a resource instance represents a specific location or a class of locations.</t>
-  </si>
-  <si>
-    <t>This is labeled as a modifier because whether or not the location is a class of locations changes how it can be used and understood.</t>
-  </si>
-  <si>
-    <t>When using a Location resource for scheduling or orders, we need to be able to refer to a class of Locations instead of a specific Location.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/location-mode|4.0.1</t>
-  </si>
-  <si>
-    <t>.playingEntity[classCode=PLC].determinerCode</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Location.type</t>
-  </si>
-  <si>
     <t>Type of function performed</t>
   </si>
   <si>
     <t>Indicates the type of function performed at the location.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.2.0</t>
   </si>
   <si>
     <t>.code</t>
@@ -959,7 +838,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.code}
+    <t xml:space="preserve">value:code}
 </t>
   </si>
   <si>
@@ -1165,43 +1044,39 @@
     <t>Location.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
+    <t xml:space="preserve">ContactPoint
 </t>
   </si>
   <si>
-    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
-  </si>
-  <si>
-    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
-  </si>
-  <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>TEL</t>
+    <t>Contact details of the location</t>
+  </si>
+  <si>
+    <t>The contact details of communication devices available at the location. This can include phone numbers, fax numbers, mobile numbers, email addresses and web sites.</t>
+  </si>
+  <si>
+    <t>.telecom</t>
   </si>
   <si>
     <t>Location.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.1.0}
+    <t xml:space="preserve">Address
 </t>
   </si>
   <si>
     <t>Adresse géopostale de la structure</t>
   </si>
   <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R4/location.html#) resource).</t>
+    <t>Physical location.</t>
+  </si>
+  <si>
+    <t>Additional addresses should be recorded using another instance of the Location resource, or via the Organization.</t>
   </si>
   <si>
     <t>If locations can be visited, we need to keep track of their address.</t>
   </si>
   <si>
-    <t>AD</t>
+    <t>.addr</t>
   </si>
   <si>
     <t>Location.physicalType</t>
@@ -1216,7 +1091,10 @@
     <t>For purposes of showing relevant locations in queries, we need to categorize locations.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-physical-type|2.1.0</t>
+    <t>Physical form of the location.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>.playingEntity [classCode=PLC].code</t>
@@ -1301,6 +1179,10 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
     <t>Organization responsible for provisioning and upkeep</t>
   </si>
   <si>
@@ -1319,7 +1201,7 @@
     <t>Location.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.1.0)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1333,105 +1215,6 @@
   </si>
   <si>
     <t>.inboundLink[typeCode=PART].source[classCode=SDLC]</t>
-  </si>
-  <si>
-    <t>Location.partOf.id</t>
-  </si>
-  <si>
-    <t>Location.partOf.extension</t>
-  </si>
-  <si>
-    <t>Location.partOf.extension:positionRoom</t>
-  </si>
-  <si>
-    <t>positionRoom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location-position-room|2.1.0}
-</t>
-  </si>
-  <si>
-    <t>FR Core Location Part Of Position Room Extension</t>
-  </si>
-  <si>
-    <t>Position of the bed in the bedroom | Position du lit dans la chambre</t>
-  </si>
-  <si>
-    <t>Location.partOf.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>Location.partOf.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>Location.partOf.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>Location.partOf.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
   </si>
   <si>
     <t>Location.hoursOfOperation</t>
@@ -1844,7 +1627,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL85"/>
+  <dimension ref="A1:AL71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.18359375" customWidth="true" bestFit="true"/>
@@ -1857,7 +1640,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="74.13671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1866,7 +1649,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
@@ -1882,7 +1665,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="58.43359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -3866,7 +3649,7 @@
         <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3926,7 +3709,7 @@
         <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>113</v>
@@ -3940,46 +3723,44 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
       </c>
@@ -4027,7 +3808,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4036,13 +3817,13 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>113</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>187</v>
+        <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
@@ -4050,14 +3831,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4070,13 +3851,13 @@
         <v>75</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>203</v>
+        <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>204</v>
@@ -4084,7 +3865,9 @@
       <c r="M21" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N21" s="2"/>
+      <c r="N21" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O21" t="s" s="2">
         <v>206</v>
       </c>
@@ -4135,7 +3918,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4147,21 +3930,21 @@
         <v>75</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>208</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4172,7 +3955,7 @@
         <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>75</v>
@@ -4181,19 +3964,21 @@
         <v>75</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>98</v>
+        <v>209</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>99</v>
+        <v>210</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>75</v>
       </c>
@@ -4241,66 +4026,64 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>101</v>
+        <v>208</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>75</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>106</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -4325,57 +4108,57 @@
         <v>75</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>75</v>
+        <v>218</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>75</v>
+        <v>219</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>75</v>
+        <v>220</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>112</v>
+        <v>215</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>75</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4392,26 +4175,22 @@
         <v>75</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>75</v>
       </c>
@@ -4435,13 +4214,13 @@
         <v>75</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>75</v>
@@ -4459,7 +4238,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4474,18 +4253,18 @@
         <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>220</v>
+        <v>102</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>75</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4493,13 +4272,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>75</v>
@@ -4508,20 +4287,18 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>222</v>
+        <v>98</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
@@ -4545,11 +4322,13 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>227</v>
+        <v>75</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4582,7 +4361,7 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>75</v>
@@ -4590,10 +4369,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4601,10 +4380,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>75</v>
@@ -4613,22 +4392,22 @@
         <v>75</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4641,7 +4420,7 @@
         <v>75</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>234</v>
+        <v>75</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>75</v>
@@ -4677,13 +4456,13 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>75</v>
@@ -4692,7 +4471,7 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>75</v>
@@ -4700,10 +4479,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4711,7 +4490,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>84</v>
@@ -4729,15 +4508,15 @@
         <v>98</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="O27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
       </c>
@@ -4749,7 +4528,7 @@
         <v>75</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>75</v>
@@ -4785,7 +4564,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4800,7 +4579,7 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>75</v>
@@ -4808,10 +4587,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4834,16 +4613,20 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
@@ -4867,13 +4650,13 @@
         <v>75</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>75</v>
+        <v>218</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>75</v>
+        <v>245</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>75</v>
+        <v>248</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>75</v>
@@ -4891,7 +4674,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4909,15 +4692,15 @@
         <v>249</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>75</v>
+        <v>250</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4928,10 +4711,10 @@
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>75</v>
@@ -4940,17 +4723,15 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N29" t="s" s="2">
         <v>254</v>
       </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4975,13 +4756,11 @@
         <v>75</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>75</v>
+        <v>255</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>75</v>
@@ -4999,13 +4778,13 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>75</v>
@@ -5017,7 +4796,7 @@
         <v>256</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>75</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -5042,19 +4821,19 @@
         <v>75</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>258</v>
+        <v>99</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>259</v>
+        <v>100</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5081,13 +4860,13 @@
         <v>75</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>260</v>
+        <v>75</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>261</v>
+        <v>75</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -5105,7 +4884,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>257</v>
+        <v>101</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5117,32 +4896,32 @@
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>262</v>
+        <v>102</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>263</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>75</v>
@@ -5151,18 +4930,20 @@
         <v>75</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>106</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
@@ -5187,57 +4968,57 @@
         <v>75</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>168</v>
+        <v>75</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>267</v>
+        <v>75</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>268</v>
+        <v>75</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>264</v>
+        <v>112</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>263</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5245,13 +5026,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>75</v>
@@ -5260,18 +5041,20 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>75</v>
       </c>
@@ -5307,25 +5090,23 @@
         <v>75</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>75</v>
@@ -5334,7 +5115,7 @@
         <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -5342,21 +5123,23 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>75</v>
@@ -5365,22 +5148,22 @@
         <v>75</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -5429,7 +5212,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5444,7 +5227,7 @@
         <v>96</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>75</v>
@@ -5452,10 +5235,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5475,21 +5258,19 @@
         <v>75</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>98</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>280</v>
+        <v>99</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>281</v>
+        <v>100</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>282</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
       </c>
@@ -5537,7 +5318,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>101</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5549,10 +5330,10 @@
         <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>283</v>
+        <v>102</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5560,21 +5341,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>75</v>
@@ -5583,23 +5364,21 @@
         <v>75</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>164</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>285</v>
+        <v>106</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>286</v>
+        <v>107</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
       </c>
@@ -5623,57 +5402,57 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>216</v>
+        <v>75</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>286</v>
+        <v>75</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>284</v>
+        <v>112</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>290</v>
+        <v>102</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>291</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5687,7 +5466,7 @@
         <v>84</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
@@ -5696,16 +5475,20 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>222</v>
+        <v>126</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
       </c>
@@ -5729,11 +5512,13 @@
         <v>75</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>295</v>
+        <v>75</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -5751,13 +5536,13 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>75</v>
@@ -5766,18 +5551,18 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>291</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5797,18 +5582,20 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>98</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>99</v>
+        <v>284</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5857,7 +5644,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>101</v>
+        <v>287</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5869,10 +5656,10 @@
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>102</v>
+        <v>288</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -5880,21 +5667,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>75</v>
@@ -5903,21 +5690,21 @@
         <v>75</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>106</v>
+        <v>291</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>75</v>
       </c>
@@ -5941,46 +5728,44 @@
         <v>75</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>75</v>
+        <v>294</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>112</v>
+        <v>295</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>102</v>
+        <v>296</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5988,10 +5773,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5999,10 +5784,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>75</v>
@@ -6014,19 +5799,17 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -6063,23 +5846,25 @@
         <v>75</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AC39" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>75</v>
@@ -6088,7 +5873,7 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -6096,20 +5881,18 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>84</v>
@@ -6124,19 +5907,19 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="O40" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -6185,13 +5968,13 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>75</v>
@@ -6200,7 +5983,7 @@
         <v>96</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -6208,12 +5991,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>75</v>
       </c>
@@ -6231,19 +6016,23 @@
         <v>75</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>99</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -6291,22 +6080,22 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>101</v>
+        <v>265</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>102</v>
+        <v>266</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6314,21 +6103,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>75</v>
@@ -6340,17 +6129,15 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6387,31 +6174,31 @@
         <v>75</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>102</v>
@@ -6422,21 +6209,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>273</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>75</v>
@@ -6445,23 +6232,21 @@
         <v>75</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>316</v>
+        <v>106</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>317</v>
+        <v>107</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
       </c>
@@ -6497,34 +6282,34 @@
         <v>75</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>320</v>
+        <v>112</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>321</v>
+        <v>102</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6532,10 +6317,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>323</v>
+        <v>275</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6558,18 +6343,20 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>324</v>
+        <v>276</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>325</v>
+        <v>277</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
       </c>
@@ -6617,7 +6404,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>327</v>
+        <v>280</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6632,7 +6419,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6640,10 +6427,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6666,18 +6453,18 @@
         <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>164</v>
+        <v>98</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>331</v>
+        <v>284</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
@@ -6701,11 +6488,13 @@
         <v>75</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>334</v>
+        <v>75</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>75</v>
@@ -6723,7 +6512,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6738,7 +6527,7 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6746,10 +6535,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6772,17 +6561,17 @@
         <v>85</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>339</v>
+        <v>291</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6807,13 +6596,11 @@
         <v>75</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>75</v>
+        <v>321</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>75</v>
@@ -6831,7 +6618,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>342</v>
+        <v>295</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6846,7 +6633,7 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>343</v>
+        <v>296</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6854,10 +6641,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6880,19 +6667,17 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>346</v>
+        <v>98</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>347</v>
+        <v>299</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -6941,7 +6726,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>351</v>
+        <v>302</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6956,7 +6741,7 @@
         <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>352</v>
+        <v>303</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6964,14 +6749,12 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>75</v>
       </c>
@@ -6992,19 +6775,19 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>142</v>
+        <v>306</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>355</v>
+        <v>307</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -7053,13 +6836,13 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>75</v>
@@ -7068,7 +6851,7 @@
         <v>96</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -7076,10 +6859,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7099,19 +6882,23 @@
         <v>75</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>98</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>99</v>
+        <v>325</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
       </c>
@@ -7159,7 +6946,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>101</v>
+        <v>329</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7171,10 +6958,10 @@
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>102</v>
+        <v>330</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
@@ -7182,14 +6969,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7208,17 +6995,15 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>105</v>
+        <v>332</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -7255,19 +7040,19 @@
         <v>75</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>112</v>
+        <v>331</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7279,21 +7064,21 @@
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>102</v>
+        <v>335</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7307,28 +7092,28 @@
         <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>126</v>
+        <v>337</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -7377,7 +7162,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7392,7 +7177,7 @@
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>75</v>
@@ -7400,10 +7185,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7426,18 +7211,18 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>98</v>
+        <v>252</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
       </c>
@@ -7461,13 +7246,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>75</v>
+        <v>347</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>75</v>
+        <v>348</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7485,7 +7270,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7500,18 +7285,18 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>75</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7531,20 +7316,20 @@
         <v>75</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>164</v>
+        <v>351</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -7569,11 +7354,13 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>361</v>
+        <v>75</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7591,7 +7378,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7606,7 +7393,7 @@
         <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>75</v>
@@ -7614,10 +7401,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7637,21 +7424,19 @@
         <v>75</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>98</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>339</v>
+        <v>99</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>340</v>
+        <v>100</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>341</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
       </c>
@@ -7699,7 +7484,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>342</v>
+        <v>101</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7711,10 +7496,10 @@
         <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>343</v>
+        <v>102</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7722,21 +7507,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>75</v>
@@ -7745,23 +7530,21 @@
         <v>75</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>346</v>
+        <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>347</v>
+        <v>106</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>348</v>
+        <v>107</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>75</v>
       </c>
@@ -7809,22 +7592,22 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>351</v>
+        <v>112</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>352</v>
+        <v>102</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7832,45 +7615,45 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>75</v>
+        <v>359</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>367</v>
+        <v>108</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>368</v>
+        <v>206</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -7919,22 +7702,22 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>370</v>
+        <v>187</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>75</v>
@@ -7942,10 +7725,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7953,10 +7736,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>75</v>
@@ -7968,13 +7751,13 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8025,33 +7808,33 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>375</v>
+        <v>96</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8059,13 +7842,13 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>75</v>
@@ -8074,20 +7857,16 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>75</v>
       </c>
@@ -8135,22 +7914,22 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>75</v>
@@ -8158,10 +7937,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8181,21 +7960,19 @@
         <v>75</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>364</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>387</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
       </c>
@@ -8219,11 +7996,13 @@
         <v>75</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>388</v>
+        <v>75</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8241,7 +8020,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8256,18 +8035,18 @@
         <v>96</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>291</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8287,20 +8066,22 @@
         <v>75</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -8349,7 +8130,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8364,7 +8145,7 @@
         <v>96</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>75</v>
@@ -8372,10 +8153,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8398,16 +8179,18 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>98</v>
+        <v>382</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>99</v>
+        <v>383</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>100</v>
+        <v>384</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>75</v>
       </c>
@@ -8455,7 +8238,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>101</v>
+        <v>381</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8467,10 +8250,10 @@
         <v>75</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>102</v>
+        <v>386</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8478,14 +8261,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8504,16 +8287,16 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>105</v>
+        <v>351</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>106</v>
+        <v>388</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>107</v>
+        <v>389</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>108</v>
+        <v>390</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8563,7 +8346,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>112</v>
+        <v>387</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8575,10 +8358,10 @@
         <v>75</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>102</v>
+        <v>391</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -8586,46 +8369,42 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>399</v>
+        <v>75</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>400</v>
+        <v>99</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>75</v>
       </c>
@@ -8673,22 +8452,22 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>402</v>
+        <v>101</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -8696,21 +8475,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>75</v>
@@ -8722,15 +8501,17 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>404</v>
+        <v>105</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>405</v>
+        <v>106</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -8779,22 +8560,22 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>403</v>
+        <v>112</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>407</v>
+        <v>102</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -8802,42 +8583,46 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>75</v>
+        <v>359</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>404</v>
+        <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>409</v>
+        <v>360</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
       </c>
@@ -8885,22 +8670,22 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>408</v>
+        <v>362</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>407</v>
+        <v>187</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>75</v>
@@ -8908,10 +8693,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8922,7 +8707,7 @@
         <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>75</v>
@@ -8934,13 +8719,13 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>404</v>
+        <v>164</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8967,13 +8752,13 @@
         <v>75</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>75</v>
+        <v>218</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>75</v>
+        <v>398</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>75</v>
+        <v>399</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>75</v>
@@ -8991,13 +8776,13 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>75</v>
@@ -9006,7 +8791,7 @@
         <v>96</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>75</v>
@@ -9014,10 +8799,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9037,23 +8822,19 @@
         <v>75</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>251</v>
+        <v>306</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
       </c>
@@ -9101,7 +8882,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9116,7 +8897,7 @@
         <v>96</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>75</v>
@@ -9124,10 +8905,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9150,18 +8931,16 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>424</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>75</v>
       </c>
@@ -9209,7 +8988,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9224,7 +9003,7 @@
         <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>75</v>
@@ -9232,10 +9011,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9258,13 +9037,13 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>98</v>
+        <v>404</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>99</v>
+        <v>408</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>100</v>
+        <v>409</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9315,7 +9094,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>101</v>
+        <v>407</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9327,10 +9106,10 @@
         <v>75</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>102</v>
+        <v>391</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9338,21 +9117,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>75</v>
@@ -9364,17 +9143,15 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>106</v>
+        <v>411</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9411,31 +9188,31 @@
         <v>75</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>112</v>
+        <v>410</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>102</v>
@@ -9446,14 +9223,12 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>75</v>
       </c>
@@ -9462,7 +9237,7 @@
         <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>75</v>
@@ -9474,16 +9249,18 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+      <c r="O71" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
       </c>
@@ -9531,7 +9308,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>112</v>
+        <v>413</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -9543,1519 +9320,17 @@
         <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AL85" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL85">
+  <autoFilter ref="A1:AL71">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11065,7 +9340,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI84">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
